--- a/extenbooks/S304_extenbook.xlsx
+++ b/extenbooks/S304_extenbook.xlsx
@@ -589,7 +589,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
@@ -620,7 +620,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -628,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6827169384198328</v>
+        <v>0.7944195543465882</v>
       </c>
     </row>
     <row r="6">
@@ -636,7 +636,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>0.6658605971504997</v>
+        <v>0.7888780354102896</v>
       </c>
     </row>
     <row r="7">
@@ -644,7 +644,7 @@
         <v>4</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6494204404299869</v>
+        <v>0.7833751716555677</v>
       </c>
     </row>
     <row r="8">
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6333861926251716</v>
+        <v>0.7779106934409975</v>
       </c>
     </row>
     <row r="9">
@@ -660,7 +660,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6177478318092168</v>
+        <v>0.7724843330060532</v>
       </c>
     </row>
     <row r="10">
@@ -668,7 +668,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6024955834975404</v>
+        <v>0.7670958244579876</v>
       </c>
     </row>
     <row r="11">
@@ -676,7 +676,7 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5876199145384451</v>
+        <v>0.761744903758804</v>
       </c>
     </row>
     <row r="12">
@@ -684,7 +684,7 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>0.5731115271545872</v>
+        <v>0.7564313087123171</v>
       </c>
     </row>
     <row r="13">
@@ -692,7 +692,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5589613531315639</v>
+        <v>0.7511547789513067</v>
       </c>
     </row>
     <row r="14">
@@ -700,7 +700,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>0.5451605481499834</v>
+        <v>0.7459150559247587</v>
       </c>
     </row>
     <row r="15">
@@ -708,7 +708,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>0.5317004862574779</v>
+        <v>0.7407118828851963</v>
       </c>
     </row>
     <row r="16">
@@ -716,7 +716,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5185727544772025</v>
+        <v>0.7355450048760998</v>
       </c>
     </row>
     <row r="17">
@@ -724,7 +724,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>0.5057691475494506</v>
+        <v>0.7304141687194127</v>
       </c>
     </row>
     <row r="18">
@@ -732,7 +732,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>0.4932816628030994</v>
+        <v>0.7253191230031368</v>
       </c>
     </row>
     <row r="19">
@@ -740,7 +740,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4811024951536805</v>
+        <v>0.7202596180690125</v>
       </c>
     </row>
     <row r="20">
@@ -748,7 +748,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4692240322249475</v>
+        <v>0.7152354060002858</v>
       </c>
     </row>
     <row r="21">
@@ -756,7 +756,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4576388495908931</v>
+        <v>0.7102462406095601</v>
       </c>
     </row>
     <row r="22">
@@ -764,7 +764,7 @@
         <v>19</v>
       </c>
       <c r="B22" t="n">
-        <v>0.4463397061352413</v>
+        <v>0.7052918774267329</v>
       </c>
     </row>
     <row r="23">
@@ -772,7 +772,7 @@
         <v>20</v>
       </c>
       <c r="B23" t="n">
-        <v>0.435319539525514</v>
+        <v>0.7003720736870169</v>
       </c>
     </row>
     <row r="24">
@@ -780,7 +780,7 @@
         <v>21</v>
       </c>
       <c r="B24" t="n">
-        <v>0.4245714617988434</v>
+        <v>0.6954865883190448</v>
       </c>
     </row>
     <row r="25">
@@ -788,7 +788,7 @@
         <v>22</v>
       </c>
       <c r="B25" t="n">
-        <v>0.4140887550567706</v>
+        <v>0.6906351819330556</v>
       </c>
     </row>
     <row r="26">
@@ -796,7 +796,7 @@
         <v>23</v>
       </c>
       <c r="B26" t="n">
-        <v>0.4038648672663406</v>
+        <v>0.6858176168091661</v>
       </c>
     </row>
     <row r="27">
@@ -804,7 +804,7 @@
         <v>24</v>
       </c>
       <c r="B27" t="n">
-        <v>0.393893408164869</v>
+        <v>0.6810336568857209</v>
       </c>
     </row>
     <row r="28">
@@ -812,7 +812,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="n">
-        <v>0.3841681452658184</v>
+        <v>0.6762830677477271</v>
       </c>
     </row>
     <row r="29">
@@ -820,7 +820,7 @@
         <v>26</v>
       </c>
       <c r="B29" t="n">
-        <v>0.3746829999632932</v>
+        <v>0.671565616615366</v>
       </c>
     </row>
     <row r="30">
@@ -828,7 +828,7 @@
         <v>27</v>
       </c>
       <c r="B30" t="n">
-        <v>0.3654320437327112</v>
+        <v>0.6668810723325883</v>
       </c>
     </row>
     <row r="31">
@@ -836,7 +836,7 @@
         <v>28</v>
       </c>
       <c r="B31" t="n">
-        <v>0.3564094944252844</v>
+        <v>0.662229205355787</v>
       </c>
     </row>
     <row r="32">
@@ -844,7 +844,7 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>0.3476097126539866</v>
+        <v>0.6576097877425493</v>
       </c>
     </row>
     <row r="33">
@@ -852,7 +852,7 @@
         <v>30</v>
       </c>
       <c r="B33" t="n">
-        <v>0.3390271982687537</v>
+        <v>0.6530225931404879</v>
       </c>
     </row>
     <row r="34">
@@ -860,7 +860,7 @@
         <v>31</v>
       </c>
       <c r="B34" t="n">
-        <v>0.3306565869187102</v>
+        <v>0.6484673967761497</v>
       </c>
     </row>
     <row r="35">
@@ -868,7 +868,7 @@
         <v>32</v>
       </c>
       <c r="B35" t="n">
-        <v>0.322492646699276</v>
+        <v>0.6439439754440013</v>
       </c>
     </row>
     <row r="36">
@@ -876,7 +876,7 @@
         <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>0.3145302748820551</v>
+        <v>0.6394521074954921</v>
       </c>
     </row>
     <row r="37">
@@ -884,7 +884,7 @@
         <v>34</v>
       </c>
       <c r="B37" t="n">
-        <v>0.3067644947254644</v>
+        <v>0.6349915728281942</v>
       </c>
     </row>
     <row r="38">
@@ -892,7 +892,7 @@
         <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>0.2991904523641086</v>
+        <v>0.6305621528750164</v>
       </c>
     </row>
     <row r="39">
@@ -900,7 +900,7 @@
         <v>36</v>
       </c>
       <c r="B39" t="n">
-        <v>0.2918034137749558</v>
+        <v>0.6261636305934946</v>
       </c>
     </row>
     <row r="40">
@@ -908,7 +908,7 @@
         <v>37</v>
       </c>
       <c r="B40" t="n">
-        <v>0.2845987618184194</v>
+        <v>0.621795790455157</v>
       </c>
     </row>
     <row r="41">
@@ -916,7 +916,7 @@
         <v>38</v>
       </c>
       <c r="B41" t="n">
-        <v>0.277571993352495</v>
+        <v>0.6174584184349627</v>
       </c>
     </row>
     <row r="42">
@@ -924,7 +924,7 @@
         <v>39</v>
       </c>
       <c r="B42" t="n">
-        <v>0.2707187164181508</v>
+        <v>0.6131513020008154</v>
       </c>
     </row>
     <row r="43">
@@ -932,7 +932,7 @@
         <v>40</v>
       </c>
       <c r="B43" t="n">
-        <v>0.2640346474942098</v>
+        <v>0.6088742301031475</v>
       </c>
     </row>
     <row r="44">
@@ -940,7 +940,7 @@
         <v>41</v>
       </c>
       <c r="B44" t="n">
-        <v>0.2575156088200096</v>
+        <v>0.6046269931645805</v>
       </c>
     </row>
     <row r="45">
@@ -948,7 +948,7 @@
         <v>42</v>
       </c>
       <c r="B45" t="n">
-        <v>0.2511575257841661</v>
+        <v>0.6004093830696544</v>
       </c>
     </row>
     <row r="46">
@@ -956,7 +956,7 @@
         <v>43</v>
       </c>
       <c r="B46" t="n">
-        <v>0.2449564243778087</v>
+        <v>0.596221193154631</v>
       </c>
     </row>
     <row r="47">
@@ -964,7 +964,7 @@
         <v>44</v>
       </c>
       <c r="B47" t="n">
-        <v>0.2389084287106956</v>
+        <v>0.5920622181973662</v>
       </c>
     </row>
     <row r="48">
@@ -972,7 +972,7 @@
         <v>45</v>
       </c>
       <c r="B48" t="n">
-        <v>0.2330097585886557</v>
+        <v>0.5879322544072551</v>
       </c>
     </row>
     <row r="49">
@@ -980,7 +980,7 @@
         <v>46</v>
       </c>
       <c r="B49" t="n">
-        <v>0.2272567271508448</v>
+        <v>0.5838310994152455</v>
       </c>
     </row>
     <row r="50">
@@ -988,7 +988,7 @@
         <v>47</v>
       </c>
       <c r="B50" t="n">
-        <v>0.2216457385653372</v>
+        <v>0.5797585522639224</v>
       </c>
     </row>
     <row r="51">
@@ -996,7 +996,7 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>0.2161732857816139</v>
+        <v>0.5757144133976604</v>
       </c>
     </row>
     <row r="52">
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="B52" t="n">
-        <v>0.2108359483385414</v>
+        <v>0.5716984846528458</v>
       </c>
     </row>
     <row r="53">
@@ -1012,7 +1012,7 @@
         <v>50</v>
       </c>
       <c r="B53" t="n">
-        <v>0.2056303902264729</v>
+        <v>0.567710569248167</v>
       </c>
     </row>
     <row r="54">
@@ -1020,7 +1020,7 @@
         <v>51</v>
       </c>
       <c r="B54" t="n">
-        <v>0.200553357802133</v>
+        <v>0.5637504717749707</v>
       </c>
     </row>
     <row r="55">
@@ -1028,7 +1028,7 @@
         <v>52</v>
       </c>
       <c r="B55" t="n">
-        <v>0.1956016777549851</v>
+        <v>0.5598179981876888</v>
       </c>
     </row>
     <row r="56">
@@ -1036,7 +1036,7 @@
         <v>53</v>
       </c>
       <c r="B56" t="n">
-        <v>0.1907722551238088</v>
+        <v>0.5559129557943285</v>
       </c>
     </row>
     <row r="57">
@@ -1044,7 +1044,7 @@
         <v>54</v>
       </c>
       <c r="B57" t="n">
-        <v>0.1860620713622486</v>
+        <v>0.5520351532470312</v>
       </c>
     </row>
     <row r="58">
@@ -1052,7 +1052,7 @@
         <v>55</v>
       </c>
       <c r="B58" t="n">
-        <v>0.181468182452124</v>
+        <v>0.5481844005326962</v>
       </c>
     </row>
     <row r="59">
@@ -1060,7 +1060,7 @@
         <v>56</v>
       </c>
       <c r="B59" t="n">
-        <v>0.1769877170633225</v>
+        <v>0.5443605089636702</v>
       </c>
     </row>
     <row r="60">
@@ -1068,7 +1068,7 @@
         <v>57</v>
       </c>
       <c r="B60" t="n">
-        <v>0.1726178747591245</v>
+        <v>0.5405632911685009</v>
       </c>
     </row>
     <row r="61">
@@ -1076,7 +1076,7 @@
         <v>58</v>
       </c>
       <c r="B61" t="n">
-        <v>0.1683559242458395</v>
+        <v>0.5367925610827567</v>
       </c>
     </row>
     <row r="62">
@@ -1084,7 +1084,7 @@
         <v>59</v>
       </c>
       <c r="B62" t="n">
-        <v>0.1641992016656583</v>
+        <v>0.5330481339399091</v>
       </c>
     </row>
     <row r="63">
@@ -1092,7 +1092,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="n">
-        <v>0.1601451089316557</v>
+        <v>0.5293298262622786</v>
       </c>
     </row>
     <row r="64">
@@ -1100,7 +1100,7 @@
         <v>61</v>
       </c>
       <c r="B64" t="n">
-        <v>0.1561911121039009</v>
+        <v>0.5256374558520455</v>
       </c>
     </row>
     <row r="65">
@@ -1108,7 +1108,7 @@
         <v>62</v>
       </c>
       <c r="B65" t="n">
-        <v>0.152334739805663</v>
+        <v>0.5219708417823203</v>
       </c>
     </row>
     <row r="66">
@@ -1116,7 +1116,7 @@
         <v>63</v>
       </c>
       <c r="B66" t="n">
-        <v>0.1485735816787201</v>
+        <v>0.5183298043882805</v>
       </c>
     </row>
     <row r="67">
@@ -1124,7 +1124,7 @@
         <v>64</v>
       </c>
       <c r="B67" t="n">
-        <v>0.1449052868768068</v>
+        <v>0.514714165258365</v>
       </c>
     </row>
     <row r="68">
@@ -1132,7 +1132,7 @@
         <v>65</v>
       </c>
       <c r="B68" t="n">
-        <v>0.1413275625962588</v>
+        <v>0.511123747225533</v>
       </c>
     </row>
     <row r="69">
@@ -1140,7 +1140,7 @@
         <v>66</v>
       </c>
       <c r="B69" t="n">
-        <v>0.1378381726429358</v>
+        <v>0.5075583743585826</v>
       </c>
     </row>
     <row r="70">
@@ -1148,7 +1148,7 @@
         <v>67</v>
       </c>
       <c r="B70" t="n">
-        <v>0.1344349360345279</v>
+        <v>0.5040178719535299</v>
       </c>
     </row>
     <row r="71">
@@ -1156,7 +1156,7 @@
         <v>68</v>
       </c>
       <c r="B71" t="n">
-        <v>0.1311157256373699</v>
+        <v>0.5005020665250486</v>
       </c>
     </row>
     <row r="72">
@@ -1164,7 +1164,7 @@
         <v>69</v>
       </c>
       <c r="B72" t="n">
-        <v>0.1278784668369142</v>
+        <v>0.4970107857979693</v>
       </c>
     </row>
     <row r="73">
@@ -1172,7 +1172,7 @@
         <v>70</v>
       </c>
       <c r="B73" t="n">
-        <v>0.1247211362410289</v>
+        <v>0.4935438586988379</v>
       </c>
     </row>
     <row r="74">
@@ -1180,7 +1180,7 @@
         <v>71</v>
       </c>
       <c r="B74" t="n">
-        <v>0.1216417604153116</v>
+        <v>0.4901011153475329</v>
       </c>
     </row>
     <row r="75">
@@ -1188,7 +1188,7 @@
         <v>72</v>
       </c>
       <c r="B75" t="n">
-        <v>0.118638414649629</v>
+        <v>0.4866823870489411</v>
       </c>
     </row>
     <row r="76">
@@ -1196,7 +1196,7 @@
         <v>73</v>
       </c>
       <c r="B76" t="n">
-        <v>0.1157092217551106</v>
+        <v>0.4832875062846917</v>
       </c>
     </row>
     <row r="77">
@@ -1204,7 +1204,7 @@
         <v>74</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1128523508908437</v>
+        <v>0.4799163067049484</v>
       </c>
     </row>
     <row r="78">
@@ -1212,7 +1212,7 @@
         <v>75</v>
       </c>
       <c r="B78" t="n">
-        <v>0.1100660164195393</v>
+        <v>0.476568623120257</v>
       </c>
     </row>
     <row r="79">
@@ -1220,7 +1220,7 @@
         <v>76</v>
       </c>
       <c r="B79" t="n">
-        <v>0.1073484767914499</v>
+        <v>0.4732442914934521</v>
       </c>
     </row>
     <row r="80">
@@ -1228,7 +1228,7 @@
         <v>77</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1046980334558445</v>
+        <v>0.4699431489316188</v>
       </c>
     </row>
     <row r="81">
@@ -1236,7 +1236,7 @@
         <v>78</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1021130297993591</v>
+        <v>0.4666650336781111</v>
       </c>
     </row>
     <row r="82">
@@ -1244,7 +1244,7 @@
         <v>79</v>
       </c>
       <c r="B82" t="n">
-        <v>0.09959185011055947</v>
+        <v>0.4634097851046257</v>
       </c>
     </row>
     <row r="83">
@@ -1252,7 +1252,7 @@
         <v>80</v>
       </c>
       <c r="B83" t="n">
-        <v>0.09713291857006866</v>
+        <v>0.4601772437033311</v>
       </c>
     </row>
     <row r="84">
@@ -1260,7 +1260,7 @@
         <v>81</v>
       </c>
       <c r="B84" t="n">
-        <v>0.09473469826562889</v>
+        <v>0.4569672510790519</v>
       </c>
     </row>
     <row r="85">
@@ -1268,7 +1268,7 @@
         <v>82</v>
       </c>
       <c r="B85" t="n">
-        <v>0.09239569023148116</v>
+        <v>0.4537796499415073</v>
       </c>
     </row>
     <row r="86">
@@ -1276,7 +1276,7 @@
         <v>83</v>
       </c>
       <c r="B86" t="n">
-        <v>0.09011443251146292</v>
+        <v>0.4506142840976037</v>
       </c>
     </row>
     <row r="87">
@@ -1284,7 +1284,7 @@
         <v>84</v>
       </c>
       <c r="B87" t="n">
-        <v>0.08788949924523803</v>
+        <v>0.4474709984437815</v>
       </c>
     </row>
     <row r="88">
@@ -1292,7 +1292,7 @@
         <v>85</v>
       </c>
       <c r="B88" t="n">
-        <v>0.08571949977708733</v>
+        <v>0.4443496389584146</v>
       </c>
     </row>
     <row r="89">
@@ -1300,7 +1300,7 @@
         <v>86</v>
       </c>
       <c r="B89" t="n">
-        <v>0.08360307778670373</v>
+        <v>0.4412500526942639</v>
       </c>
     </row>
     <row r="90">
@@ -1308,7 +1308,7 @@
         <v>87</v>
       </c>
       <c r="B90" t="n">
-        <v>0.08153891044144787</v>
+        <v>0.438172087770982</v>
       </c>
     </row>
     <row r="91">
@@ -1316,7 +1316,7 @@
         <v>88</v>
       </c>
       <c r="B91" t="n">
-        <v>0.07952570756953459</v>
+        <v>0.435115593367672</v>
       </c>
     </row>
     <row r="92">
@@ -1324,7 +1324,7 @@
         <v>89</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0775622108536337</v>
+        <v>0.4320804197154965</v>
       </c>
     </row>
     <row r="93">
@@ -1332,7 +1332,7 @@
         <v>90</v>
       </c>
       <c r="B93" t="n">
-        <v>0.07564719304438047</v>
+        <v>0.4290664180903394</v>
       </c>
     </row>
     <row r="94">
@@ -1340,7 +1340,7 @@
         <v>91</v>
       </c>
       <c r="B94" t="n">
-        <v>0.07377945719330503</v>
+        <v>0.4260734408055178</v>
       </c>
     </row>
     <row r="95">
@@ -1348,7 +1348,7 @@
         <v>92</v>
       </c>
       <c r="B95" t="n">
-        <v>0.07195783590470048</v>
+        <v>0.423101341204546</v>
       </c>
     </row>
     <row r="96">
@@ -1356,7 +1356,7 @@
         <v>93</v>
       </c>
       <c r="B96" t="n">
-        <v>0.07018119060596259</v>
+        <v>0.4201499736539489</v>
       </c>
     </row>
     <row r="97">
@@ -1364,7 +1364,7 @@
         <v>94</v>
       </c>
       <c r="B97" t="n">
-        <v>0.06844841083594502</v>
+        <v>0.417219193536126</v>
       </c>
     </row>
     <row r="98">
@@ -1372,7 +1372,7 @@
         <v>95</v>
       </c>
       <c r="B98" t="n">
-        <v>0.06675841355088473</v>
+        <v>0.4143088572422651</v>
       </c>
     </row>
     <row r="99">
@@ -1380,7 +1380,7 @@
         <v>96</v>
       </c>
       <c r="B99" t="n">
-        <v>0.06511014244746444</v>
+        <v>0.4114188221653056</v>
       </c>
     </row>
     <row r="100">
@@ -1388,7 +1388,7 @@
         <v>97</v>
       </c>
       <c r="B100" t="n">
-        <v>0.06350256730258873</v>
+        <v>0.4085489466929503</v>
       </c>
     </row>
     <row r="101">
@@ -1396,7 +1396,7 @@
         <v>98</v>
       </c>
       <c r="B101" t="n">
-        <v>0.06193468332946109</v>
+        <v>0.4056990902007269</v>
       </c>
     </row>
     <row r="102">
@@ -1404,7 +1404,7 @@
         <v>99</v>
       </c>
       <c r="B102" t="n">
-        <v>0.06040551054955935</v>
+        <v>0.4028691130450971</v>
       </c>
     </row>
     <row r="103">
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="B103" t="n">
-        <v>0.05891409318011725</v>
+        <v>0.4000588765566141</v>
       </c>
     </row>
     <row r="104">
@@ -1420,7 +1420,7 @@
         <v>101</v>
       </c>
       <c r="B104" t="n">
-        <v>0.05745949903672916</v>
+        <v>0.3972682430331276</v>
       </c>
     </row>
     <row r="105">
@@ -1428,7 +1428,7 @@
         <v>102</v>
       </c>
       <c r="B105" t="n">
-        <v>0.05604081895070435</v>
+        <v>0.3944970757330366</v>
       </c>
     </row>
     <row r="106">
@@ -1436,7 +1436,7 @@
         <v>103</v>
       </c>
       <c r="B106" t="n">
-        <v>0.05465716620080718</v>
+        <v>0.391745238868589</v>
       </c>
     </row>
     <row r="107">
@@ -1444,7 +1444,7 @@
         <v>104</v>
       </c>
       <c r="B107" t="n">
-        <v>0.05330767595902722</v>
+        <v>0.3890125975992277</v>
       </c>
     </row>
     <row r="108">
@@ -1452,7 +1452,7 @@
         <v>105</v>
       </c>
       <c r="B108" t="n">
-        <v>0.05199150475003371</v>
+        <v>0.3862990180249838</v>
       </c>
     </row>
     <row r="109">
@@ -1460,7 +1460,7 @@
         <v>106</v>
       </c>
       <c r="B109" t="n">
-        <v>0.05070782992397602</v>
+        <v>0.3836043671799153</v>
       </c>
     </row>
     <row r="110">
@@ -1468,7 +1468,7 @@
         <v>107</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0494558491423007</v>
+        <v>0.3809285130255916</v>
       </c>
     </row>
     <row r="111">
@@ -1476,7 +1476,7 @@
         <v>108</v>
       </c>
       <c r="B111" t="n">
-        <v>0.04823477987626379</v>
+        <v>0.3782713244446236</v>
       </c>
     </row>
     <row r="112">
@@ -1484,7 +1484,7 @@
         <v>109</v>
       </c>
       <c r="B112" t="n">
-        <v>0.04704385891782482</v>
+        <v>0.3756326712342394</v>
       </c>
     </row>
     <row r="113">
@@ -1492,7 +1492,7 @@
         <v>110</v>
       </c>
       <c r="B113" t="n">
-        <v>0.04588234190261703</v>
+        <v>0.3730124240999037</v>
       </c>
     </row>
     <row r="114">
@@ -1500,7 +1500,7 @@
         <v>111</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0447495028446953</v>
+        <v>0.3704104546489825</v>
       </c>
     </row>
     <row r="115">
@@ -1508,7 +1508,7 @@
         <v>112</v>
       </c>
       <c r="B115" t="n">
-        <v>0.04364463368277138</v>
+        <v>0.3678266353844521</v>
       </c>
     </row>
     <row r="116">
@@ -1516,7 +1516,7 @@
         <v>113</v>
       </c>
       <c r="B116" t="n">
-        <v>0.04256704383765256</v>
+        <v>0.3652608396986518</v>
       </c>
     </row>
     <row r="117">
@@ -1524,7 +1524,7 @@
         <v>114</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0415160597806071</v>
+        <v>0.3627129418670794</v>
       </c>
     </row>
     <row r="118">
@@ -1532,7 +1532,7 @@
         <v>115</v>
       </c>
       <c r="B118" t="n">
-        <v>0.04049102461238692</v>
+        <v>0.3601828170422314</v>
       </c>
     </row>
     <row r="119">
@@ -1540,7 +1540,7 @@
         <v>116</v>
       </c>
       <c r="B119" t="n">
-        <v>0.03949129765264414</v>
+        <v>0.3576703412474851</v>
       </c>
     </row>
     <row r="120">
@@ -1548,7 +1548,7 @@
         <v>117</v>
       </c>
       <c r="B120" t="n">
-        <v>0.03851625403948505</v>
+        <v>0.3551753913710241</v>
       </c>
     </row>
     <row r="121">
@@ -1556,7 +1556,7 @@
         <v>118</v>
       </c>
       <c r="B121" t="n">
-        <v>0.03756528433891107</v>
+        <v>0.3526978451598049</v>
       </c>
     </row>
     <row r="122">
@@ -1564,7 +1564,7 @@
         <v>119</v>
       </c>
       <c r="B122" t="n">
-        <v>0.03663779416390266</v>
+        <v>0.3502375812135677</v>
       </c>
     </row>
     <row r="123">
@@ -1572,7 +1572,7 @@
         <v>120</v>
       </c>
       <c r="B123" t="n">
-        <v>0.03573320380290807</v>
+        <v>0.3477944789788868</v>
       </c>
     </row>
     <row r="124">
@@ -1580,7 +1580,7 @@
         <v>121</v>
       </c>
       <c r="B124" t="n">
-        <v>0.03485094785750476</v>
+        <v>0.3453684187432638</v>
       </c>
     </row>
     <row r="125"/>
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="B130" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>2</v>
       </c>
       <c r="B131" t="n">
-        <v>0.6827169384198328</v>
+        <v>0.7944195543465882</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>3</v>
       </c>
       <c r="B132" t="n">
-        <v>0.6658605971504997</v>
+        <v>0.7888780354102896</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>4</v>
       </c>
       <c r="B133" t="n">
-        <v>0.6494204404299869</v>
+        <v>0.7833751716555677</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         <v>5</v>
       </c>
       <c r="B134" t="n">
-        <v>0.6333861926251716</v>
+        <v>0.7779106934409975</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>6</v>
       </c>
       <c r="B135" t="n">
-        <v>0.6177478318092168</v>
+        <v>0.7724843330060532</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>7</v>
       </c>
       <c r="B136" t="n">
-        <v>0.6024955834975404</v>
+        <v>0.7670958244579876</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="n">
-        <v>0.5876199145384451</v>
+        <v>0.761744903758804</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>9</v>
       </c>
       <c r="B138" t="n">
-        <v>0.5731115271545872</v>
+        <v>0.7564313087123171</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>10</v>
       </c>
       <c r="B139" t="n">
-        <v>0.5589613531315639</v>
+        <v>0.7511547789513067</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>11</v>
       </c>
       <c r="B140" t="n">
-        <v>0.5451605481499834</v>
+        <v>0.7459150559247587</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -1878,7 +1878,7 @@
         <v>12</v>
       </c>
       <c r="B141" t="n">
-        <v>0.5317004862574779</v>
+        <v>0.7407118828851963</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>13</v>
       </c>
       <c r="B142" t="n">
-        <v>0.5185727544772025</v>
+        <v>0.7355450048760998</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="n">
-        <v>0.5057691475494506</v>
+        <v>0.7304141687194127</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="n">
-        <v>0.4932816628030994</v>
+        <v>0.7253191230031368</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         <v>16</v>
       </c>
       <c r="B145" t="n">
-        <v>0.4811024951536805</v>
+        <v>0.7202596180690125</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>17</v>
       </c>
       <c r="B146" t="n">
-        <v>0.4692240322249475</v>
+        <v>0.7152354060002858</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         <v>18</v>
       </c>
       <c r="B147" t="n">
-        <v>0.4576388495908931</v>
+        <v>0.7102462406095601</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
         <v>19</v>
       </c>
       <c r="B148" t="n">
-        <v>0.4463397061352413</v>
+        <v>0.7052918774267329</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>20</v>
       </c>
       <c r="B149" t="n">
-        <v>0.435319539525514</v>
+        <v>0.7003720736870169</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>21</v>
       </c>
       <c r="B150" t="n">
-        <v>0.4245714617988434</v>
+        <v>0.6954865883190448</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>22</v>
       </c>
       <c r="B151" t="n">
-        <v>0.4140887550567706</v>
+        <v>0.6906351819330556</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -2131,7 +2131,7 @@
         <v>23</v>
       </c>
       <c r="B152" t="n">
-        <v>0.4038648672663406</v>
+        <v>0.6858176168091661</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>24</v>
       </c>
       <c r="B153" t="n">
-        <v>0.393893408164869</v>
+        <v>0.6810336568857209</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>25</v>
       </c>
       <c r="B154" t="n">
-        <v>0.3841681452658184</v>
+        <v>0.6762830677477271</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -2200,7 +2200,7 @@
         <v>26</v>
       </c>
       <c r="B155" t="n">
-        <v>0.3746829999632932</v>
+        <v>0.671565616615366</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -2223,7 +2223,7 @@
         <v>27</v>
       </c>
       <c r="B156" t="n">
-        <v>0.3654320437327112</v>
+        <v>0.6668810723325883</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>28</v>
       </c>
       <c r="B157" t="n">
-        <v>0.3564094944252844</v>
+        <v>0.662229205355787</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>29</v>
       </c>
       <c r="B158" t="n">
-        <v>0.3476097126539866</v>
+        <v>0.6576097877425493</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>30</v>
       </c>
       <c r="B159" t="n">
-        <v>0.3390271982687537</v>
+        <v>0.6530225931404879</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>31</v>
       </c>
       <c r="B160" t="n">
-        <v>0.3306565869187102</v>
+        <v>0.6484673967761497</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>32</v>
       </c>
       <c r="B161" t="n">
-        <v>0.322492646699276</v>
+        <v>0.6439439754440013</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -2361,7 +2361,7 @@
         <v>33</v>
       </c>
       <c r="B162" t="n">
-        <v>0.3145302748820551</v>
+        <v>0.6394521074954921</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>34</v>
       </c>
       <c r="B163" t="n">
-        <v>0.3067644947254644</v>
+        <v>0.6349915728281942</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>35</v>
       </c>
       <c r="B164" t="n">
-        <v>0.2991904523641086</v>
+        <v>0.6305621528750164</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>36</v>
       </c>
       <c r="B165" t="n">
-        <v>0.2918034137749558</v>
+        <v>0.6261636305934946</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>37</v>
       </c>
       <c r="B166" t="n">
-        <v>0.2845987618184194</v>
+        <v>0.621795790455157</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>38</v>
       </c>
       <c r="B167" t="n">
-        <v>0.277571993352495</v>
+        <v>0.6174584184349627</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>39</v>
       </c>
       <c r="B168" t="n">
-        <v>0.2707187164181508</v>
+        <v>0.6131513020008154</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>40</v>
       </c>
       <c r="B169" t="n">
-        <v>0.2640346474942098</v>
+        <v>0.6088742301031475</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>41</v>
       </c>
       <c r="B170" t="n">
-        <v>0.2575156088200096</v>
+        <v>0.6046269931645805</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>42</v>
       </c>
       <c r="B171" t="n">
-        <v>0.2511575257841661</v>
+        <v>0.6004093830696544</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         <v>43</v>
       </c>
       <c r="B172" t="n">
-        <v>0.2449564243778087</v>
+        <v>0.596221193154631</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -2614,7 +2614,7 @@
         <v>44</v>
       </c>
       <c r="B173" t="n">
-        <v>0.2389084287106956</v>
+        <v>0.5920622181973662</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45</v>
       </c>
       <c r="B174" t="n">
-        <v>0.2330097585886557</v>
+        <v>0.5879322544072551</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -2660,7 +2660,7 @@
         <v>46</v>
       </c>
       <c r="B175" t="n">
-        <v>0.2272567271508448</v>
+        <v>0.5838310994152455</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
         <v>47</v>
       </c>
       <c r="B176" t="n">
-        <v>0.2216457385653372</v>
+        <v>0.5797585522639224</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>48</v>
       </c>
       <c r="B177" t="n">
-        <v>0.2161732857816139</v>
+        <v>0.5757144133976604</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>49</v>
       </c>
       <c r="B178" t="n">
-        <v>0.2108359483385414</v>
+        <v>0.5716984846528458</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -2752,7 +2752,7 @@
         <v>50</v>
       </c>
       <c r="B179" t="n">
-        <v>0.2056303902264729</v>
+        <v>0.567710569248167</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -2775,7 +2775,7 @@
         <v>51</v>
       </c>
       <c r="B180" t="n">
-        <v>0.200553357802133</v>
+        <v>0.5637504717749707</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
         <v>52</v>
       </c>
       <c r="B181" t="n">
-        <v>0.1956016777549851</v>
+        <v>0.5598179981876888</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>53</v>
       </c>
       <c r="B182" t="n">
-        <v>0.1907722551238088</v>
+        <v>0.5559129557943285</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -2844,7 +2844,7 @@
         <v>54</v>
       </c>
       <c r="B183" t="n">
-        <v>0.1860620713622486</v>
+        <v>0.5520351532470312</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -2867,7 +2867,7 @@
         <v>55</v>
       </c>
       <c r="B184" t="n">
-        <v>0.181468182452124</v>
+        <v>0.5481844005326962</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>56</v>
       </c>
       <c r="B185" t="n">
-        <v>0.1769877170633225</v>
+        <v>0.5443605089636702</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>57</v>
       </c>
       <c r="B186" t="n">
-        <v>0.1726178747591245</v>
+        <v>0.5405632911685009</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>58</v>
       </c>
       <c r="B187" t="n">
-        <v>0.1683559242458395</v>
+        <v>0.5367925610827567</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>59</v>
       </c>
       <c r="B188" t="n">
-        <v>0.1641992016656583</v>
+        <v>0.5330481339399091</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>60</v>
       </c>
       <c r="B189" t="n">
-        <v>0.1601451089316557</v>
+        <v>0.5293298262622786</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>61</v>
       </c>
       <c r="B190" t="n">
-        <v>0.1561911121039009</v>
+        <v>0.5256374558520455</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>62</v>
       </c>
       <c r="B191" t="n">
-        <v>0.152334739805663</v>
+        <v>0.5219708417823203</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>63</v>
       </c>
       <c r="B192" t="n">
-        <v>0.1485735816787201</v>
+        <v>0.5183298043882805</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>64</v>
       </c>
       <c r="B193" t="n">
-        <v>0.1449052868768068</v>
+        <v>0.514714165258365</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>65</v>
       </c>
       <c r="B194" t="n">
-        <v>0.1413275625962588</v>
+        <v>0.511123747225533</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
         <v>66</v>
       </c>
       <c r="B195" t="n">
-        <v>0.1378381726429358</v>
+        <v>0.5075583743585826</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>67</v>
       </c>
       <c r="B196" t="n">
-        <v>0.1344349360345279</v>
+        <v>0.5040178719535299</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>68</v>
       </c>
       <c r="B197" t="n">
-        <v>0.1311157256373699</v>
+        <v>0.5005020665250486</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>69</v>
       </c>
       <c r="B198" t="n">
-        <v>0.1278784668369142</v>
+        <v>0.4970107857979693</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>70</v>
       </c>
       <c r="B199" t="n">
-        <v>0.1247211362410289</v>
+        <v>0.4935438586988379</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
         <v>71</v>
       </c>
       <c r="B200" t="n">
-        <v>0.1216417604153116</v>
+        <v>0.4901011153475329</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>72</v>
       </c>
       <c r="B201" t="n">
-        <v>0.118638414649629</v>
+        <v>0.4866823870489411</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         <v>73</v>
       </c>
       <c r="B202" t="n">
-        <v>0.1157092217551106</v>
+        <v>0.4832875062846917</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>74</v>
       </c>
       <c r="B203" t="n">
-        <v>0.1128523508908437</v>
+        <v>0.4799163067049484</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>75</v>
       </c>
       <c r="B204" t="n">
-        <v>0.1100660164195393</v>
+        <v>0.476568623120257</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>76</v>
       </c>
       <c r="B205" t="n">
-        <v>0.1073484767914499</v>
+        <v>0.4732442914934521</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>77</v>
       </c>
       <c r="B206" t="n">
-        <v>0.1046980334558445</v>
+        <v>0.4699431489316188</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>78</v>
       </c>
       <c r="B207" t="n">
-        <v>0.1021130297993591</v>
+        <v>0.4666650336781111</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
         <v>79</v>
       </c>
       <c r="B208" t="n">
-        <v>0.09959185011055947</v>
+        <v>0.4634097851046257</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
         <v>80</v>
       </c>
       <c r="B209" t="n">
-        <v>0.09713291857006866</v>
+        <v>0.4601772437033311</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>81</v>
       </c>
       <c r="B210" t="n">
-        <v>0.09473469826562889</v>
+        <v>0.4569672510790519</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>82</v>
       </c>
       <c r="B211" t="n">
-        <v>0.09239569023148116</v>
+        <v>0.4537796499415073</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         <v>83</v>
       </c>
       <c r="B212" t="n">
-        <v>0.09011443251146292</v>
+        <v>0.4506142840976037</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>84</v>
       </c>
       <c r="B213" t="n">
-        <v>0.08788949924523803</v>
+        <v>0.4474709984437815</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>85</v>
       </c>
       <c r="B214" t="n">
-        <v>0.08571949977708733</v>
+        <v>0.4443496389584146</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
         <v>86</v>
       </c>
       <c r="B215" t="n">
-        <v>0.08360307778670373</v>
+        <v>0.4412500526942639</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>87</v>
       </c>
       <c r="B216" t="n">
-        <v>0.08153891044144787</v>
+        <v>0.438172087770982</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>88</v>
       </c>
       <c r="B217" t="n">
-        <v>0.07952570756953459</v>
+        <v>0.435115593367672</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>89</v>
       </c>
       <c r="B218" t="n">
-        <v>0.0775622108536337</v>
+        <v>0.4320804197154965</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>90</v>
       </c>
       <c r="B219" t="n">
-        <v>0.07564719304438047</v>
+        <v>0.4290664180903394</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -3695,7 +3695,7 @@
         <v>91</v>
       </c>
       <c r="B220" t="n">
-        <v>0.07377945719330503</v>
+        <v>0.4260734408055178</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>92</v>
       </c>
       <c r="B221" t="n">
-        <v>0.07195783590470048</v>
+        <v>0.423101341204546</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>93</v>
       </c>
       <c r="B222" t="n">
-        <v>0.07018119060596259</v>
+        <v>0.4201499736539489</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -3764,7 +3764,7 @@
         <v>94</v>
       </c>
       <c r="B223" t="n">
-        <v>0.06844841083594502</v>
+        <v>0.417219193536126</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>95</v>
       </c>
       <c r="B224" t="n">
-        <v>0.06675841355088473</v>
+        <v>0.4143088572422651</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>96</v>
       </c>
       <c r="B225" t="n">
-        <v>0.06511014244746444</v>
+        <v>0.4114188221653056</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>97</v>
       </c>
       <c r="B226" t="n">
-        <v>0.06350256730258873</v>
+        <v>0.4085489466929503</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>98</v>
       </c>
       <c r="B227" t="n">
-        <v>0.06193468332946109</v>
+        <v>0.4056990902007269</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -3879,7 +3879,7 @@
         <v>99</v>
       </c>
       <c r="B228" t="n">
-        <v>0.06040551054955935</v>
+        <v>0.4028691130450971</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -3902,7 +3902,7 @@
         <v>100</v>
       </c>
       <c r="B229" t="n">
-        <v>0.05891409318011725</v>
+        <v>0.4000588765566141</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>101</v>
       </c>
       <c r="B230" t="n">
-        <v>0.05745949903672916</v>
+        <v>0.3972682430331276</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>102</v>
       </c>
       <c r="B231" t="n">
-        <v>0.05604081895070435</v>
+        <v>0.3944970757330366</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>103</v>
       </c>
       <c r="B232" t="n">
-        <v>0.05465716620080718</v>
+        <v>0.391745238868589</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>104</v>
       </c>
       <c r="B233" t="n">
-        <v>0.05330767595902722</v>
+        <v>0.3890125975992277</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>105</v>
       </c>
       <c r="B234" t="n">
-        <v>0.05199150475003371</v>
+        <v>0.3862990180249838</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>106</v>
       </c>
       <c r="B235" t="n">
-        <v>0.05070782992397602</v>
+        <v>0.3836043671799153</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>107</v>
       </c>
       <c r="B236" t="n">
-        <v>0.0494558491423007</v>
+        <v>0.3809285130255916</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -4086,7 +4086,7 @@
         <v>108</v>
       </c>
       <c r="B237" t="n">
-        <v>0.04823477987626379</v>
+        <v>0.3782713244446236</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>109</v>
       </c>
       <c r="B238" t="n">
-        <v>0.04704385891782482</v>
+        <v>0.3756326712342394</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>110</v>
       </c>
       <c r="B239" t="n">
-        <v>0.04588234190261703</v>
+        <v>0.3730124240999037</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>111</v>
       </c>
       <c r="B240" t="n">
-        <v>0.0447495028446953</v>
+        <v>0.3704104546489825</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -4178,7 +4178,7 @@
         <v>112</v>
       </c>
       <c r="B241" t="n">
-        <v>0.04364463368277138</v>
+        <v>0.3678266353844521</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         <v>113</v>
       </c>
       <c r="B242" t="n">
-        <v>0.04256704383765256</v>
+        <v>0.3652608396986518</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>114</v>
       </c>
       <c r="B243" t="n">
-        <v>0.0415160597806071</v>
+        <v>0.3627129418670794</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>115</v>
       </c>
       <c r="B244" t="n">
-        <v>0.04049102461238692</v>
+        <v>0.3601828170422314</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         <v>116</v>
       </c>
       <c r="B245" t="n">
-        <v>0.03949129765264414</v>
+        <v>0.3576703412474851</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -4293,7 +4293,7 @@
         <v>117</v>
       </c>
       <c r="B246" t="n">
-        <v>0.03851625403948505</v>
+        <v>0.3551753913710241</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>118</v>
       </c>
       <c r="B247" t="n">
-        <v>0.03756528433891107</v>
+        <v>0.3526978451598049</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>119</v>
       </c>
       <c r="B248" t="n">
-        <v>0.03663779416390266</v>
+        <v>0.3502375812135677</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         <v>120</v>
       </c>
       <c r="B249" t="n">
-        <v>0.03573320380290807</v>
+        <v>0.3477944789788868</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>121</v>
       </c>
       <c r="B250" t="n">
-        <v>0.03485094785750476</v>
+        <v>0.3453684187432638</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -4468,7 +4468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -5312,7 +5312,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.229927</v>
+        <v>0.151645</v>
       </c>
     </row>
     <row r="17">
@@ -5322,7 +5322,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.365149</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18">
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>91.287263</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-18T22:01:50.364264+00:00</t>
+          <t>2026-05-27T05:08:16.208438+00:00</t>
         </is>
       </c>
     </row>
@@ -5404,11 +5404,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5431,88 +5431,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Discretionary Propensity to Consume, Case II</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S304_research.json", "adequacy_report": "Technical/docs/chapters/CH3_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S304_DPR.md", "epr": "Technical/docs/series/S304_EPR.md", "loader": "Technical/code/L01_loaders/L01_S304_load.py", "processor": "Technical/code/P02_processors/P02_S304_construct.py", "validator": "Technical/code/V03_validators/V03_S304_validate.py", "processed": "Technical/data/processed/S304.parquet", "chopped_csv": "Technical/chopped/S304.csv", "extenbook_xlsx": "Technical/extenbooks/S304_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S304-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2016_EQ_3_4_3_11"]</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S304_extenbook.xlsx
+++ b/extenbooks/S304_extenbook.xlsx
@@ -4415,7 +4415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -4454,7 +4454,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Record type**: Data Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Author**: opus-subagent-wave-a-ch3 (Phase 5-8 fanout)</t>
+          <t>**Prepared by**: RSCD data-construction pipeline</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>- Research dossier: `Technical/research/S304_research.json`</t>
+          <t>- Series research notes: `Technical/research/S304_research.json`</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>## 3. Sources</t>
+          <t>## From the Book</t>
         </is>
       </c>
     </row>
@@ -4594,244 +4594,240 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>&gt; The same result obtains if instead c declines with discretionary income. To see this, we rewrite equation (3.4) as (p1x1 - p1x1min) = c (y - p1x1min), which is a linear relationship between discretionary expenditure on necessary goods and discretionary income. Since c is the slope of this curve, as c falls the curve gets flatter.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>&gt; -- Shaikh (2016), Chapter 3, p. 93 &lt;!-- kb: ch03, p.93 (ch03_micro_foundations.md, Case II) --&gt;</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>| **S304-A** | n/a (theoretical) | Shaikh 2016 eq (3.4) framework, p. 91; Figure 3.6 axis bounds p. 94 | dimensionless | analytic regeneration from chosen c(y) form |</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## 3. Sources</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1. Income grid y in [0, 60], 121 points.</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2. Calibration: c(y) = c0 * exp(-k*y) with c0 = 0.7, k = 0.05. At y=0, c = 0.7; at y=60, c ~ 0.035.</t>
+          <t>| **S304-A** (the dataset's single data column) | n/a (theoretical) | Shaikh 2016 eq (3.4) framework, p. 91; Figure 3.6 axis bounds p. 94 | dimensionless | analytic regeneration from chosen c(y) form |</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>3. Functional form chosen as the simplest monotone-declining curve that hits the axis bounds [0.0, 0.8] of Fig 3.6.</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>**Formula**: `c(y) = c0 * exp(-k * y)`</t>
-        </is>
-      </c>
+      <c r="A41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1. Income grid y in [0, 60], 121 points.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>2. Calibration: c(y) = c0 * exp(-k*y) with c0 = 0.7, k = 0.05. At y=0, c = 0.7; at y=60, c ~ 0.035.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3. Functional form chosen as the simplest monotone-declining curve that hits the axis bounds [0.0, 0.8] of Fig 3.6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>**Formula**: `c(y) = c0 * exp(-k * y)`</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>- **No year dimension**.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>## 6. Units</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>- **Output**: discretionary propensity c, dimensionless.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>## 7. Caveats</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-    </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1. Functional form for c(y) is NOT stated in the book. Shaikh shows the qualitative shape (declining), not the exact analytical form. We use exponential decay as the simplest one-parameter family that matches the axis range. Disclosed in EPR.</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2. Alternative reasonable forms (linear, power-law) would give similar qualitative behaviour; the validator's shape check is the binding test.</t>
+          <t>- **Output**: discretionary propensity c, dimensionless.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>3. No empirical content; no proxy; no synthetic fill.</t>
-        </is>
-      </c>
+      <c r="A55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>## 7. Caveats</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>## 8. Cross-references</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1. Functional form for c(y) is NOT stated in the book. Shaikh shows the qualitative shape (declining), not the exact analytical form. We use exponential decay as the simplest one-parameter family that matches the axis range. Disclosed in EPR.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>- **CD legacy ID**: none</t>
+          <t>2. Alternative reasonable forms (linear, power-law) would give similar qualitative behaviour; the validator's shape check is the binding test.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.6 on p. 94</t>
+          <t>3. No empirical content; no proxy; no synthetic fill.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.6</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>## 8. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>## 9. Validation expectation</t>
-        </is>
-      </c>
+      <c r="A63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>- **Predecessor series**: none (first constructed in this dataset).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>- **Tolerance**: PASS_THEORETICAL mode. Checks: monotone declining, all values within [0.0, 0.8] (Fig 3.6 axis bounds).</t>
+          <t>- **Book reference**: Shaikh (2016), Ch. 3, Fig3.6 on p. 94</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>- **Knowledge Base**: `SalvagedInputs/figures_reference/HDARP_SERIES_LINKAGE.json` -&gt; Fig3.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>- **Source-book text**: Shaikh (2016) Chapter 3, extracted in the project knowledge base (ch03_micro_foundations.md).</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4">
+      <c r="A68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>- **Tolerance**: the validator's theoretical-curve mode (checks the curve's shape and bounds rather than matching tabulated values). Checks: monotone declining, all values within [0.0, 0.8] (Fig 3.6 axis bounds).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4">
         <f>== EPR: S304_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t># S304 -- Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>**Series**: S304 -- Discretionary Propensity to Consume, Case II</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>**Content type**: `theoretical`</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>**Related**: `S304_DPR.md`, `Technical/research/S304_research.json`</t>
+          <t># S304 -- Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -4841,27 +4837,35 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Series**: S304 -- Discretionary Propensity to Consume, Case II</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>**Record type**: Extension Provenance Record</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>## 1. Classification</t>
+          <t>**Content type**: `theoretical`</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>**Authored**: 2026-05-18</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>`theoretical`; c(y) declining functional form (Case II setup).</t>
+          <t>**Related**: `S304_DPR.md`, `Technical/research/S304_research.json`</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4875,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4885,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>**Extension method**: `none`. Re-evaluated each run.</t>
+          <t>## 1. Classification</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4895,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>## 3. Worked example</t>
+          <t>`theoretical`; c(y) declining functional form (Case II setup).</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4905,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Pass-through; c(0) = 0.7, c(60) ~ 0.035. Monotone declining.</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4915,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>## 4. No-Proxy disclosure</t>
+          <t>**Extension method**: `none`. Re-evaluated each time the data-loading step runs.</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4925,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>No proxy substitution. See `S304_DPR.md` for source details.</t>
+          <t>## 3. Worked example</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4935,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>## 5. No-Synthetic disclosure</t>
+          <t>Pass-through; c(0) = 0.7, c(60) ~ 0.035. Monotone declining.</t>
         </is>
       </c>
     </row>
@@ -4941,86 +4945,109 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>No synthetic gap-filling in the prohibited sense. The DPR documents any</t>
+          <t>## 4. No-Proxy disclosure</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>analytic regeneration or library-data dependence explicitly.</t>
-        </is>
-      </c>
+      <c r="A98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>No proxy substitution. See `S304_DPR.md` for source details.</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
+      <c r="A100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>## 5. No-Synthetic disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>No synthetic gap-filling in the prohibited sense. The companion Data Provenance Record (DPR) documents any analytic regeneration or library-data dependence explicitly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
         <is>
           <t>## 6. Failure-mode table</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
         <is>
           <t>Form choice (exponential vs alternative); bound violation; shape failure.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>## 7. CD2 divergence pre-disclosure</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>No CD2 predecessor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>## 8. Why no API extension applies</t>
-        </is>
-      </c>
+      <c r="A108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>## 7. Predecessor divergence pre-disclosure</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
-        </is>
-      </c>
+      <c r="A110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>Predecessor series: none (first constructed in this dataset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>## 8. Why no API extension applies</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>This series has no time dimension (theoretical/cross_sectional). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>Anu-framework rule on extension only applies to `time_series` series. The</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>chopped CSV is the final published deliverable.</t>
         </is>
@@ -5214,7 +5241,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5377,7 +5404,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-05-27T05:08:16.208438+00:00</t>
+          <t>2026-07-02T06:22:11.926870+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S304_extenbook.xlsx
+++ b/extenbooks/S304_extenbook.xlsx
@@ -4468,7 +4468,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Status**: theoretical_validated</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-02T06:22:11.926870+00:00</t>
+          <t>2026-07-11T03:44:24.666379+00:00</t>
         </is>
       </c>
     </row>
@@ -5431,11 +5431,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5458,6 +5458,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2016_EQ_3_4_3_11</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>theoretical_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Renderable analytic curve (Shaikh Fig 3.6): the discretionary propensity c declining with income under Case II, 121 clean points. Renders as an x-y curve over the income grid ('year' index column, NOT calendar years). L01/P02 exist; replicate.py builds it (PASS). Caveat: Case II calibration is illustrative (DPR); shape, not level, is the faithful object. KB coverage: ch03 IS extracted in the book KB (HDARP v3.3 Sraffa OCR campaign) (Body_Text/ch03_micro_foundations.md + Figures/ch03/ch03_fig_3.6.md); the chapter-3 figure quotes in the research JSON ARE verifiable against KB, and a 'From the book' section can be populated in the explainer (doc-side backfill).", "date": "2026-06-10"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S304_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S304_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Theoretical curve; no historical observations. Calibrated to match the printed axis bounds of the figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>theoretical</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>discretionary propensity c (dimensionless)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
